--- a/data/trans_orig/barthel-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/barthel-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de dependencia funcional para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Puntuación media de la escala de dependencia funcional para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,8; 98,02</t>
+          <t>93,65; 97,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,85; 98,57</t>
+          <t>93,83; 98,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91,7; 96,66</t>
+          <t>91,39; 96,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,19; 97,02</t>
+          <t>93,99; 97,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,84; 97,72</t>
+          <t>92,27; 97,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,53; 94,68</t>
+          <t>89,56; 94,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,85; 95,48</t>
+          <t>90,95; 95,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>89,54; 92,8</t>
+          <t>89,48; 92,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,14; 97,45</t>
+          <t>94,11; 97,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92,54; 96,06</t>
+          <t>92,57; 95,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92,36; 95,68</t>
+          <t>92,34; 95,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,19; 94,37</t>
+          <t>92,04; 94,36</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,82; 98,4</t>
+          <t>94,52; 98,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,06; 95,71</t>
+          <t>89,81; 95,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,48; 97,48</t>
+          <t>93,4; 97,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,87; 97,03</t>
+          <t>93,72; 96,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,54; 96,69</t>
+          <t>92,16; 96,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,56; 91,5</t>
+          <t>86,11; 91,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,31; 95,65</t>
+          <t>90,89; 95,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,77; 93,18</t>
+          <t>89,51; 92,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>94,45; 97,15</t>
+          <t>94,35; 97,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88,25; 92,75</t>
+          <t>88,65; 92,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92,84; 96,08</t>
+          <t>92,41; 96,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,91; 94,29</t>
+          <t>91,96; 94,27</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>96,89; 99,46</t>
+          <t>96,9; 99,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,37; 97,19</t>
+          <t>88,71; 97,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,28; 98,14</t>
+          <t>94,57; 98,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94,81; 97,92</t>
+          <t>94,82; 97,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,08; 97,54</t>
+          <t>93,11; 97,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,21; 92,89</t>
+          <t>85,15; 93,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,22; 94,16</t>
+          <t>87,52; 94,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,39; 99,2</t>
+          <t>92,32; 99,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95,54; 98,15</t>
+          <t>95,34; 98,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88,51; 94,24</t>
+          <t>88,43; 94,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91,21; 95,48</t>
+          <t>91,27; 95,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,34; 98,96</t>
+          <t>94,38; 99,04</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,38; 98,91</t>
+          <t>95,62; 98,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,02; 97,44</t>
+          <t>92,97; 97,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95,74; 98,56</t>
+          <t>95,58; 98,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95,72; 97,8</t>
+          <t>95,67; 97,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,69; 97,06</t>
+          <t>93,6; 97,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,75; 95,18</t>
+          <t>90,8; 95,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,69; 96,26</t>
+          <t>92,61; 96,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,78; 94,54</t>
+          <t>91,69; 94,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>94,87; 97,54</t>
+          <t>95,06; 97,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,67; 95,66</t>
+          <t>92,76; 95,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94,54; 96,81</t>
+          <t>94,39; 96,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,9; 95,73</t>
+          <t>93,89; 95,64</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>96,28; 98,04</t>
+          <t>96,43; 98,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,51; 96,26</t>
+          <t>93,78; 96,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95,12; 97,0</t>
+          <t>95,22; 97,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95,61; 96,91</t>
+          <t>95,55; 96,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,41; 96,51</t>
+          <t>94,39; 96,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,78; 92,64</t>
+          <t>89,75; 92,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,27; 94,69</t>
+          <t>92,21; 94,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,05; 96,47</t>
+          <t>92,04; 96,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95,6; 96,98</t>
+          <t>95,54; 96,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91,91; 93,85</t>
+          <t>91,85; 93,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93,8; 95,39</t>
+          <t>93,88; 95,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,93; 96,49</t>
+          <t>93,89; 96,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/barthel-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/barthel-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95,78</t>
+          <t>96,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91,37</t>
+          <t>91,48</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,36</t>
+          <t>93,58</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,65; 97,82</t>
+          <t>93,97; 97,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,83; 98,54</t>
+          <t>93,57; 98,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91,39; 96,44</t>
+          <t>91,87; 96,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93,99; 97,05</t>
+          <t>94,43; 97,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,27; 97,72</t>
+          <t>92,39; 97,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,56; 94,68</t>
+          <t>89,71; 94,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,95; 95,59</t>
+          <t>91,2; 95,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>89,48; 92,71</t>
+          <t>89,81; 92,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,11; 97,42</t>
+          <t>93,98; 97,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92,57; 95,85</t>
+          <t>92,35; 95,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92,34; 95,61</t>
+          <t>92,39; 95,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,04; 94,36</t>
+          <t>92,38; 94,57</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95,55</t>
+          <t>95,75</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91,51</t>
+          <t>91,68</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,22</t>
+          <t>93,41</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,52; 98,38</t>
+          <t>95,07; 98,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,81; 95,73</t>
+          <t>89,77; 95,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,4; 97,35</t>
+          <t>93,28; 97,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,72; 96,87</t>
+          <t>93,95; 96,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,16; 96,69</t>
+          <t>92,45; 96,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,11; 91,99</t>
+          <t>85,73; 91,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,89; 95,76</t>
+          <t>90,33; 95,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,51; 92,95</t>
+          <t>89,86; 93,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>94,35; 97,18</t>
+          <t>94,18; 97,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88,65; 92,81</t>
+          <t>88,63; 92,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92,41; 96,0</t>
+          <t>92,82; 96,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,96; 94,27</t>
+          <t>92,11; 94,47</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96,81</t>
+          <t>96,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96,95</t>
+          <t>93,07</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,91</t>
+          <t>94,9</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>96,9; 99,39</t>
+          <t>96,82; 99,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,71; 97,25</t>
+          <t>88,56; 97,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,57; 98,11</t>
+          <t>94,38; 98,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94,82; 97,89</t>
+          <t>95,23; 97,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,11; 97,48</t>
+          <t>93,1; 97,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,15; 93,09</t>
+          <t>85,4; 93,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,52; 94,39</t>
+          <t>87,37; 94,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,32; 99,22</t>
+          <t>90,86; 94,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95,34; 98,12</t>
+          <t>95,47; 98,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88,43; 94,05</t>
+          <t>88,89; 94,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91,27; 95,49</t>
+          <t>90,84; 95,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,38; 99,04</t>
+          <t>93,45; 95,92</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96,95</t>
+          <t>96,92</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>93,26</t>
+          <t>92,92</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,84</t>
+          <t>94,61</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,62; 98,81</t>
+          <t>95,35; 98,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,97; 97,46</t>
+          <t>93,06; 97,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95,58; 98,55</t>
+          <t>95,62; 98,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95,67; 97,68</t>
+          <t>95,68; 97,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,6; 97,07</t>
+          <t>93,61; 97,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,8; 95,31</t>
+          <t>90,79; 95,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,61; 96,23</t>
+          <t>92,35; 96,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,69; 94,37</t>
+          <t>91,19; 94,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,06; 97,53</t>
+          <t>95,17; 97,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,76; 95,73</t>
+          <t>92,48; 95,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94,39; 96,78</t>
+          <t>94,38; 96,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,89; 95,64</t>
+          <t>93,55; 95,52</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96,31</t>
+          <t>96,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93,85</t>
+          <t>92,31</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,8</t>
+          <t>94,13</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>96,43; 98,09</t>
+          <t>96,54; 98,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,78; 96,3</t>
+          <t>93,51; 96,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95,22; 97,02</t>
+          <t>95,15; 96,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95,55; 96,93</t>
+          <t>95,72; 96,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,39; 96,43</t>
+          <t>94,3; 96,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,75; 92,58</t>
+          <t>89,94; 92,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,21; 94,73</t>
+          <t>92,25; 94,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,04; 96,69</t>
+          <t>91,45; 93,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95,54; 96,95</t>
+          <t>95,63; 96,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91,85; 93,82</t>
+          <t>92,0; 93,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93,88; 95,48</t>
+          <t>93,97; 95,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,89; 96,64</t>
+          <t>93,55; 94,65</t>
         </is>
       </c>
     </row>
